--- a/MonteCarloApp/simulaciones/resultados/OpenMP_C++_metricas.xlsx
+++ b/MonteCarloApp/simulaciones/resultados/OpenMP_C++_metricas.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04620647430419922</v>
+        <v>0.01658987998962402</v>
       </c>
       <c r="C2" t="n">
-        <v>156.21875</v>
+        <v>153.55078125</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
     </row>
   </sheetData>
